--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1838,17 +1838,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3261.2</t>
+          <t>1239.3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1858,52 +1858,53 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3322.3</t>
+          <t>1252.4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54/506</t>
+          <t>13/506</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3208.6</t>
+          <t>1230.9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>197/506</t>
+          <t>188/506</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2650.7</t>
+          <t>1073.0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>149/506</t>
+          <t>93/506</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2854.3</t>
+          <t>1154.4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>RLSOnePlusOne</t>
+          <t>SVMMetaModelLogNor
+mal</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3316.5</t>
+          <t>1233.8</t>
         </is>
       </c>
     </row>
@@ -1920,73 +1921,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>15/506</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3261.2</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3322.3</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>54/506</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3208.6</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>197/506</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2650.7</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>149/506</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2854.3</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>RLSOnePlusOne</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2642.4</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2665.1</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>36/506</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2597.5</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>209/506</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2219.0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>135/506</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2391.5</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteLengler2On
-ePlusOne</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2617.0</t>
+          <t>3316.5</t>
         </is>
       </c>
     </row>
@@ -2003,71 +2003,154 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2642.4</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2665.1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36/506</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2597.5</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>209/506</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2219.0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>135/506</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2391.5</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteLengler2On
+ePlusOne</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2617.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>14/506</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2584.4</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2625.5</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>42/506</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2557.0</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>186/506</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>142/506</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2349.2</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>SVM1MetaModelLogNo
 rmal</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>2605.1</t>
         </is>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -934,17 +934,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.7156</t>
+          <t>0.7449</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -954,135 +954,135 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.7194</t>
+          <t>0.7502</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0.7171</t>
+          <t>0.7336</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>386/506</t>
+          <t>105/506</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0.5798</t>
+          <t>0.7007</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391/506</t>
+          <t>180/506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0.5730</t>
+          <t>0.6895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>LognormalDiscreteO
-nePlusOne</t>
+          <t>MetaModelFmin2</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.7166</t>
+          <t>0.7295</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5/506</t>
+          <t>40/506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205.7</t>
+          <t>0.7156</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0.7194</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0.7171</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>386/506</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0.5798</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>391/506</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0.5730</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>LognormalDiscreteO
+nePlusOne</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>206.2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>63/506</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>199.8</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>251/506</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188.2</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>269/506</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>184.6</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>208.4</t>
+          <t>0.7166</t>
         </is>
       </c>
     </row>
@@ -1099,62 +1099,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>5/506</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>206.2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92/506</t>
+          <t>63/506</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>199.8</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>135/506</t>
+          <t>251/506</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>188.2</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141/506</t>
+          <t>269/506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145.4</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>208.4</t>
         </is>
       </c>
     </row>
@@ -1181,62 +1181,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>8/506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90/506</t>
+          <t>92/506</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>139.1</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>120/506</t>
+          <t>135/506</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155/506</t>
+          <t>141/506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>145.4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>143.4</t>
+          <t>154.3</t>
         </is>
       </c>
     </row>
@@ -1263,62 +1263,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12/506</t>
+          <t>6/506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>426.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>428.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91/506</t>
+          <t>90/506</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>410.4</t>
+          <t>139.1</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>266/506</t>
+          <t>120/506</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>379.4</t>
+          <t>137.6</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>268/506</t>
+          <t>155/506</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>377.5</t>
+          <t>137.4</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>438.1</t>
+          <t>143.4</t>
         </is>
       </c>
     </row>
@@ -1340,62 +1340,62 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36/505</t>
+          <t>12/506</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>581.8</t>
+          <t>426.3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5/505</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>585.4</t>
+          <t>428.3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66/505</t>
+          <t>91/506</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>570.8</t>
+          <t>410.4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>257/505</t>
+          <t>266/506</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>504.4</t>
+          <t>379.4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225/505</t>
+          <t>268/506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>517.2</t>
+          <t>377.5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/506</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>588.7</t>
+          <t>438.1</t>
         </is>
       </c>
     </row>
@@ -1427,57 +1427,57 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47/506</t>
+          <t>36/505</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1196.5</t>
+          <t>581.8</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>5/505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1209.3</t>
+          <t>585.4</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80/506</t>
+          <t>66/505</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1177.9</t>
+          <t>570.8</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>259/506</t>
+          <t>257/505</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1034.7</t>
+          <t>504.4</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255/506</t>
+          <t>225/505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1046.1</t>
+          <t>517.2</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1/506</t>
+          <t>1/505</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1216.2</t>
+          <t>588.7</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>47/506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>955.4</t>
+          <t>1196.5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1529,27 +1529,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>961.0</t>
+          <t>1209.3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18/506</t>
+          <t>80/506</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>934.5</t>
+          <t>1177.9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>267/506</t>
+          <t>259/506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>842.8</t>
+          <t>1034.7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>857.3</t>
+          <t>1046.1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>1216.2</t>
         </is>
       </c>
     </row>
@@ -1591,62 +1591,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>918.2</t>
+          <t>955.4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>923.9</t>
+          <t>961.0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55/506</t>
+          <t>18/506</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>907.6</t>
+          <t>934.5</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>265/506</t>
+          <t>267/506</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>817.2</t>
+          <t>842.8</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251/506</t>
+          <t>255/506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>830.9</t>
+          <t>857.3</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>928.6</t>
+          <t>964.9</t>
         </is>
       </c>
     </row>
@@ -1668,77 +1668,77 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>11/506</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1608.4</t>
+          <t>918.2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>923.9</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55/506</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>907.6</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>265/506</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>817.2</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>251/506</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>830.9</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>CMAL3</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1643.6</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>47/506</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1570.4</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>200/506</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1317.4</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>100/506</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1422.4</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>NLOPT_LN_PRAXIS</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1607.1</t>
+          <t>928.6</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1305.6</t>
+          <t>1608.4</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1775,43 +1775,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1310.9</t>
+          <t>1643.6</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>47/506</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1290.5</t>
+          <t>1570.4</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>198/506</t>
+          <t>200/506</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1105.2</t>
+          <t>1317.4</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93/506</t>
+          <t>100/506</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>1422.4</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>BigLognormalDiscre
-teOnePlusOne</t>
+          <t>NLOPT_LN_PRAXIS</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1821,7 +1820,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1301.4</t>
+          <t>1607.1</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1837,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1848,7 +1847,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1239.3</t>
+          <t>1305.6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1858,27 +1857,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1252.4</t>
+          <t>1310.9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1230.9</t>
+          <t>1290.5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>188/506</t>
+          <t>198/506</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1073.0</t>
+          <t>1105.2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1888,13 +1887,13 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1154.4</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>SVMMetaModelLogNor
-mal</t>
+          <t>BigLognormalDiscre
+teOnePlusOne</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1904,7 +1903,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1233.8</t>
+          <t>1301.4</t>
         </is>
       </c>
     </row>
@@ -1921,17 +1920,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3261.2</t>
+          <t>1239.3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1941,52 +1940,53 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3322.3</t>
+          <t>1252.4</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54/506</t>
+          <t>13/506</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3208.6</t>
+          <t>1230.9</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>197/506</t>
+          <t>188/506</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2650.7</t>
+          <t>1073.0</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149/506</t>
+          <t>93/506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2854.3</t>
+          <t>1154.4</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>RLSOnePlusOne</t>
+          <t>SVMMetaModelLogNor
+mal</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3316.5</t>
+          <t>1233.8</t>
         </is>
       </c>
     </row>
@@ -2003,73 +2003,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>15/506</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3261.2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3322.3</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>54/506</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3208.6</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>197/506</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2650.7</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>149/506</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2854.3</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>RLSOnePlusOne</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>2642.4</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2665.1</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>36/506</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2597.5</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>209/506</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>2219.0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>135/506</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2391.5</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteLengler2On
-ePlusOne</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2617.0</t>
+          <t>3316.5</t>
         </is>
       </c>
     </row>
@@ -2086,71 +2085,154 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2642.4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2665.1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36/506</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2597.5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>209/506</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2219.0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>135/506</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2391.5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteLengler2On
+ePlusOne</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2617.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>14/506</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2584.4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2625.5</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>42/506</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2557.0</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>186/506</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>142/506</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2349.2</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>SVM1MetaModelLogNo
 rmal</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>2605.1</t>
         </is>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -616,62 +616,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7588</t>
+          <t>0.7124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0.7125</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53/506</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0.7096</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>128/506</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0.7050</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>238/506</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0.7009</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>CMApara</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0.7581</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42/506</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0.7463</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148/506</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0.7330</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>181/506</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0.7311</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0.7658</t>
+          <t>0.7119</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7561</t>
+          <t>0.7476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -708,42 +708,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0.7582</t>
+          <t>0.7477</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>59/506</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0.7465</t>
+          <t>0.7391</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>204/506</t>
+          <t>148/506</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0.7191</t>
+          <t>0.7317</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126/506</t>
+          <t>206/506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0.7252</t>
+          <t>0.7274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0.7471</t>
+          <t>0.7459</t>
         </is>
       </c>
     </row>
@@ -765,62 +765,62 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0.7588</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0.7309</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2/506</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0.7357</t>
+          <t>0.7581</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>42/506</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0.7266</t>
+          <t>0.7463</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>357/506</t>
+          <t>148/506</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0.6372</t>
+          <t>0.7330</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>389/506</t>
+          <t>181/506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0.6071</t>
+          <t>0.7311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0.7430</t>
+          <t>0.7658</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7339</t>
+          <t>0.7561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -872,52 +872,52 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.7359</t>
+          <t>0.7582</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4/506</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0.7465</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>204/506</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0.7191</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>126/506</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0.7252</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0.7249</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99/506</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0.7004</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61/506</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0.7100</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>MetaModelFmin2</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.7218</t>
+          <t>0.7471</t>
         </is>
       </c>
     </row>
@@ -929,77 +929,77 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0.7309</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0.7449</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0.7357</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4/506</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0.7266</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>357/506</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0.6372</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>389/506</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0.6071</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0.7502</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0.7336</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105/506</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0.7007</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>180/506</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0.6895</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>MetaModelFmin2</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.7295</t>
+          <t>0.7430</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7156</t>
+          <t>0.7339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1036,217 +1036,217 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.7194</t>
+          <t>0.7359</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0.7171</t>
+          <t>0.7249</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>386/506</t>
+          <t>99/506</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0.5798</t>
+          <t>0.7004</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>391/506</t>
+          <t>61/506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0.5730</t>
+          <t>0.7100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>LognormalDiscreteO
-nePlusOne</t>
+          <t>MetaModelFmin2</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.7166</t>
+          <t>0.7218</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205.7</t>
+          <t>0.7449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0.7502</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>206.2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63/506</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>199.8</t>
+          <t>0.7336</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>251/506</t>
+          <t>105/506</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188.2</t>
+          <t>0.7007</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269/506</t>
+          <t>180/506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>0.6895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>MetaModelFmin2</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>208.4</t>
+          <t>0.7295</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>40/506</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0.7156</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0.7194</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8/506</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>153.8</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92/506</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>0.7171</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>135/506</t>
+          <t>386/506</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>0.5798</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141/506</t>
+          <t>391/506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145.4</t>
+          <t>0.5730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>LognormalDiscreteO
+nePlusOne</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>0.7166</t>
         </is>
       </c>
     </row>
@@ -1263,17 +1263,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6/506</t>
+          <t>5/506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1283,42 +1283,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>206.2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90/506</t>
+          <t>63/506</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>139.1</t>
+          <t>199.8</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>120/506</t>
+          <t>251/506</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>137.6</t>
+          <t>188.2</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155/506</t>
+          <t>269/506</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>143.4</t>
+          <t>208.4</t>
         </is>
       </c>
     </row>
@@ -1345,62 +1345,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>426.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>8/506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>428.3</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91/506</t>
+          <t>92/506</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>410.4</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>266/506</t>
+          <t>135/506</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>379.4</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>268/506</t>
+          <t>141/506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>377.5</t>
+          <t>145.4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>438.1</t>
+          <t>154.3</t>
         </is>
       </c>
     </row>
@@ -1422,77 +1422,77 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36/505</t>
+          <t>6/506</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581.8</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5/505</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>585.4</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66/505</t>
+          <t>90/506</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>570.8</t>
+          <t>139.1</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>257/505</t>
+          <t>120/506</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>504.4</t>
+          <t>137.6</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225/505</t>
+          <t>155/506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>517.2</t>
+          <t>137.4</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/506</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>588.7</t>
+          <t>143.4</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1514,52 +1514,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47/506</t>
+          <t>12/506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1196.5</t>
+          <t>426.3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1209.3</t>
+          <t>428.3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80/506</t>
+          <t>91/506</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1177.9</t>
+          <t>410.4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>259/506</t>
+          <t>266/506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1034.7</t>
+          <t>379.4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>255/506</t>
+          <t>268/506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1046.1</t>
+          <t>377.5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1216.2</t>
+          <t>438.1</t>
         </is>
       </c>
     </row>
@@ -1591,72 +1591,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>36/505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>955.4</t>
+          <t>581.8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>5/505</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>961.0</t>
+          <t>585.4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18/506</t>
+          <t>66/505</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>934.5</t>
+          <t>570.8</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>267/506</t>
+          <t>257/505</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>842.8</t>
+          <t>504.4</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255/506</t>
+          <t>225/505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>857.3</t>
+          <t>517.2</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1/506</t>
+          <t>1/505</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>588.7</t>
         </is>
       </c>
     </row>
@@ -1673,62 +1673,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>918.2</t>
+          <t>451.1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>923.9</t>
+          <t>452.7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55/506</t>
+          <t>22/506</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>907.6</t>
+          <t>438.3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>265/506</t>
+          <t>243/506</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>817.2</t>
+          <t>408.4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251/506</t>
+          <t>228/506</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>830.9</t>
+          <t>413.0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>928.6</t>
+          <t>453.8</t>
         </is>
       </c>
     </row>
@@ -1750,77 +1750,77 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>47/506</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1196.5</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1608.4</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1209.3</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>80/506</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1177.9</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>259/506</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1034.7</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>255/506</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1046.1</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1643.6</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>47/506</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1570.4</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>200/506</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1317.4</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>100/506</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1422.4</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>NLOPT_LN_PRAXIS</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1607.1</t>
+          <t>1216.2</t>
         </is>
       </c>
     </row>
@@ -1832,78 +1832,77 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>955.4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1305.6</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>961.0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18/506</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>934.5</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>267/506</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>842.8</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>255/506</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>857.3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>CMApara</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1310.9</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1290.5</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>198/506</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1105.2</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>93/506</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1197.0</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>BigLognormalDiscre
-teOnePlusOne</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1301.4</t>
+          <t>964.9</t>
         </is>
       </c>
     </row>
@@ -1915,78 +1914,77 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>11/506</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1239.3</t>
+          <t>918.2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>923.9</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>55/506</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>907.6</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>265/506</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>817.2</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>251/506</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>830.9</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>CMAL3</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1252.4</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13/506</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1230.9</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>188/506</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1073.0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>93/506</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1154.4</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>SVMMetaModelLogNor
-mal</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1233.8</t>
+          <t>928.6</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2001,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3261.2</t>
+          <t>1608.4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2023,52 +2021,52 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3322.3</t>
+          <t>1643.6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54/506</t>
+          <t>47/506</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3208.6</t>
+          <t>1570.4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>197/506</t>
+          <t>200/506</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2650.7</t>
+          <t>1317.4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149/506</t>
+          <t>100/506</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2854.3</t>
+          <t>1422.4</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>RLSOnePlusOne</t>
+          <t>NLOPT_LN_PRAXIS</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3316.5</t>
+          <t>1607.1</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2083,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2095,7 +2093,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2642.4</t>
+          <t>1305.6</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2105,43 +2103,43 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2665.1</t>
+          <t>1310.9</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36/506</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2597.5</t>
+          <t>1290.5</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>209/506</t>
+          <t>198/506</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2219.0</t>
+          <t>1105.2</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135/506</t>
+          <t>93/506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2391.5</t>
+          <t>1197.0</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>DiscreteLengler2On
-ePlusOne</t>
+          <t>BigLognormalDiscre
+teOnePlusOne</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2151,7 +2149,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2617.0</t>
+          <t>1301.4</t>
         </is>
       </c>
     </row>
@@ -2168,71 +2166,319 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1239.3</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1252.4</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13/506</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1230.9</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>188/506</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1073.0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>93/506</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1154.4</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>SVMMetaModelLogNor
+mal</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1233.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15/506</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3261.2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3322.3</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>54/506</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3208.6</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>197/506</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2650.7</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>149/506</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2854.3</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>RLSOnePlusOne</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3316.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2642.4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2665.1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>36/506</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2597.5</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>209/506</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2219.0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>135/506</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2391.5</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteLengler2On
+ePlusOne</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2617.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>14/506</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2584.4</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2625.5</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>42/506</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2557.0</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>186/506</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>142/506</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2349.2</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>SVM1MetaModelLogNo
 rmal</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>2605.1</t>
         </is>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -847,77 +847,77 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>12/506</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7561</t>
+          <t>0.7424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>5/506</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0.7453</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36/506</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0.7330</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>264/506</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0.7088</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>310/506</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0.6932</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0.7582</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0.7465</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>204/506</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0.7191</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>126/506</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0.7252</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.7471</t>
+          <t>0.7602</t>
         </is>
       </c>
     </row>
@@ -934,72 +934,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0.7561</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0.7582</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4/506</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0.7465</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>204/506</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0.7191</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>126/506</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0.7252</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0.7309</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2/506</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0.7357</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0.7266</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>357/506</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0.6372</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>389/506</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0.6071</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.7430</t>
+          <t>0.7471</t>
         </is>
       </c>
     </row>
@@ -1011,77 +1011,77 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0.7309</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0.7339</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0.7357</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4/506</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0.7266</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>357/506</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0.6372</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>389/506</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0.6071</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Tabu</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0.7359</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0.7249</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>99/506</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0.7004</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>61/506</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0.7100</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>MetaModelFmin2</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4/506</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.7218</t>
+          <t>0.7430</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7449</t>
+          <t>0.7339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.7502</t>
+          <t>0.7359</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1128,27 +1128,27 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0.7336</t>
+          <t>0.7249</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>105/506</t>
+          <t>99/506</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0.7007</t>
+          <t>0.7004</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180/506</t>
+          <t>61/506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0.6895</t>
+          <t>0.7100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0.7295</t>
+          <t>0.7218</t>
         </is>
       </c>
     </row>
@@ -1180,155 +1180,155 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0.7449</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0.7502</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0.7336</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>105/506</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0.7007</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>180/506</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0.6895</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>MetaModelFmin2</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>4/506</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>0.7295</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NK</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>40/506</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0.7156</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0.7194</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0.7171</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>386/506</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>0.5798</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>391/506</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0.5730</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>LognormalDiscreteO
 nePlusOne</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>0.7166</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5/506</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>205.7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>206.2</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>63/506</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>199.8</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>251/506</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188.2</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>269/506</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>184.6</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Tabu</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>208.4</t>
         </is>
       </c>
     </row>
@@ -1345,62 +1345,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>5/506</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>205.7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>153.8</t>
+          <t>206.2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92/506</t>
+          <t>63/506</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>199.8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>135/506</t>
+          <t>251/506</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>188.2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141/506</t>
+          <t>269/506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145.4</t>
+          <t>184.6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>208.4</t>
         </is>
       </c>
     </row>
@@ -1427,62 +1427,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>8/506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>153.8</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90/506</t>
+          <t>92/506</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>139.1</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>120/506</t>
+          <t>135/506</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>137.6</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155/506</t>
+          <t>141/506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>145.4</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>143.4</t>
+          <t>154.3</t>
         </is>
       </c>
     </row>
@@ -1509,62 +1509,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12/506</t>
+          <t>6/506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>426.3</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>428.3</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91/506</t>
+          <t>90/506</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>410.4</t>
+          <t>139.1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>266/506</t>
+          <t>120/506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>379.4</t>
+          <t>137.6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>268/506</t>
+          <t>155/506</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>377.5</t>
+          <t>137.4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>438.1</t>
+          <t>143.4</t>
         </is>
       </c>
     </row>
@@ -1586,62 +1586,62 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36/505</t>
+          <t>12/506</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>581.8</t>
+          <t>426.3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5/505</t>
+          <t>4/506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>585.4</t>
+          <t>428.3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66/505</t>
+          <t>91/506</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>570.8</t>
+          <t>410.4</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>257/505</t>
+          <t>266/506</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>504.4</t>
+          <t>379.4</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225/505</t>
+          <t>268/506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>517.2</t>
+          <t>377.5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/506</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>588.7</t>
+          <t>438.1</t>
         </is>
       </c>
     </row>
@@ -1673,72 +1673,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>36/505</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451.1</t>
+          <t>581.8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2/506</t>
+          <t>5/505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>452.7</t>
+          <t>585.4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22/506</t>
+          <t>66/505</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>438.3</t>
+          <t>570.8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>243/506</t>
+          <t>257/505</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>408.4</t>
+          <t>504.4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>228/506</t>
+          <t>225/505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>517.2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1/506</t>
+          <t>1/505</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>453.8</t>
+          <t>588.7</t>
         </is>
       </c>
     </row>
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47/506</t>
+          <t>3/506</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1196.5</t>
+          <t>451.1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1775,42 +1775,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1209.3</t>
+          <t>452.7</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80/506</t>
+          <t>22/506</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1177.9</t>
+          <t>438.3</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>259/506</t>
+          <t>243/506</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1034.7</t>
+          <t>408.4</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>255/506</t>
+          <t>228/506</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1046.1</t>
+          <t>413.0</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>CMApara</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1216.2</t>
+          <t>453.8</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1847,62 +1847,62 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>955.4</t>
+          <t>433.9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20/506</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>427.5</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>239/506</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>398.9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>224/506</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>403.7</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>CMAL3</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>961.0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18/506</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>934.5</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>267/506</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>842.8</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>255/506</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>857.3</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>CMApara</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1/506</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>435.4</t>
         </is>
       </c>
     </row>
@@ -1919,62 +1919,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11/506</t>
+          <t>47/506</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>918.2</t>
+          <t>1196.5</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3/506</t>
+          <t>2/506</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>923.9</t>
+          <t>1209.3</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55/506</t>
+          <t>80/506</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>907.6</t>
+          <t>1177.9</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>265/506</t>
+          <t>259/506</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>817.2</t>
+          <t>1034.7</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251/506</t>
+          <t>255/506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>830.9</t>
+          <t>1046.1</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>Tabu</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>928.6</t>
+          <t>1216.2</t>
         </is>
       </c>
     </row>
@@ -1996,77 +1996,77 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>955.4</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1608.4</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>961.0</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>18/506</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>934.5</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>267/506</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>842.8</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>255/506</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>857.3</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>CMApara</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1643.6</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>47/506</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1570.4</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>200/506</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1317.4</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>100/506</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1422.4</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>NLOPT_LN_PRAXIS</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>3/506</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1607.1</t>
+          <t>964.9</t>
         </is>
       </c>
     </row>
@@ -2078,407 +2078,571 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11/506</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>918.2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>923.9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>55/506</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>907.6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>265/506</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>817.2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>251/506</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>830.9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>CMAL3</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>928.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2/506</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1608.4</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1/506</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1643.6</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>47/506</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1570.4</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>200/506</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1317.4</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>100/506</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1422.4</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>NLOPT_LN_PRAXIS</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>3/506</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1607.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1305.6</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1310.9</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>4/506</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>1290.5</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>198/506</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>1105.2</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>93/506</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>1197.0</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>BigLognormalDiscre
 teOnePlusOne</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>1301.4</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1239.3</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1252.4</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>13/506</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1230.9</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>188/506</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1073.0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>93/506</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>1154.4</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>SVMMetaModelLogNor
 mal</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>1233.8</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>15/506</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>3261.2</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>3322.3</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>54/506</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>3208.6</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>197/506</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2650.7</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>149/506</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2854.3</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>RLSOnePlusOne</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>3316.5</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>2642.4</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2665.1</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>36/506</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>2597.5</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>209/506</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>2219.0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>135/506</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2391.5</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>DiscreteLengler2On
 ePlusOne</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>3/506</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>2617.0</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>14/506</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>2584.4</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1/506</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2625.5</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2610.6</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>42/506</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>2557.0</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>186/506</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2206.6</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>142/506</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2349.2</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>SVM1MetaModelLogNo
 rmal</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>2/506</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>2605.1</t>
         </is>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -591,12 +591,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6/505</t>
+          <t>20/505</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7111</t>
+          <t>0.7106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7/505</t>
+          <t>14/505</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7437</t>
+          <t>0.7429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24/505</t>
+          <t>22/505</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.7500</t>
+          <t>0.7504</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12/505</t>
+          <t>15/505</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7413</t>
+          <t>0.7396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7358</t>
+          <t>0.7344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7552</t>
+          <t>0.7555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.7330</t>
+          <t>0.7353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.7074</t>
+          <t>0.7072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.7349</t>
+          <t>0.7343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.7481</t>
+          <t>0.7477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.7205</t>
+          <t>0.7248</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>125/505</t>
+          <t>103/505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197.3</t>
+          <t>198.2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>109/505</t>
+          <t>140/505</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146.9</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>134/505</t>
+          <t>133/505</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140/505</t>
+          <t>139/505</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128/505</t>
+          <t>164/505</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>137.1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>154/505</t>
+          <t>153/505</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86/505</t>
+          <t>80/505</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>410.6</t>
+          <t>411.1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>126/505</t>
+          <t>130/505</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324.1</t>
+          <t>323.6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88/505</t>
+          <t>138/505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>308.5</t>
+          <t>304.4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>45/504</t>
+          <t>47/504</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>577.1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40/505</t>
+          <t>30/505</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433.6</t>
+          <t>436.5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59/505</t>
+          <t>29/505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>420.8</t>
+          <t>425.0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>55/505</t>
+          <t>48/505</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1189.5</t>
+          <t>1193.3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10/505</t>
+          <t>19/505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>936.4</t>
+          <t>932.9</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17/505</t>
+          <t>16/505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29/505</t>
+          <t>20/505</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>912.6</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1622.4</t>
+          <t>1623.5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1290.8</t>
+          <t>1300.4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1247.2</t>
+          <t>1234.7</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3296.7</t>
+          <t>3285.9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>1/505</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2612.2</t>
+          <t>2633.4</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>2/505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12/505</t>
+          <t>1/505</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2586.0</t>
+          <t>2606.9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>2/505</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20/505</t>
+          <t>20/504</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52/505</t>
+          <t>52/504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>127/505</t>
+          <t>126/504</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>237/505</t>
+          <t>236/504</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14/505</t>
+          <t>13/504</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58/505</t>
+          <t>57/504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>147/505</t>
+          <t>146/504</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>205/505</t>
+          <t>204/504</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22/505</t>
+          <t>21/504</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41/505</t>
+          <t>40/504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147/505</t>
+          <t>146/504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>180/505</t>
+          <t>179/504</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -775,17 +775,18 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>ChainCMAwithMetaRe
+centeringsqrt</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.7658</t>
+          <t>0.7565</t>
         </is>
       </c>
     </row>
@@ -807,7 +808,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15/505</t>
+          <t>14/504</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -817,7 +818,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35/505</t>
+          <t>34/504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +828,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>263/505</t>
+          <t>262/504</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -837,7 +838,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>309/505</t>
+          <t>308/504</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -847,17 +848,18 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>ChainCMAwithLHSsqr
+t</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0.7602</t>
+          <t>0.7493</t>
         </is>
       </c>
     </row>
@@ -879,7 +881,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -889,7 +891,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4/505</t>
+          <t>4/504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -899,7 +901,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>159/505</t>
+          <t>158/504</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -909,7 +911,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>207/505</t>
+          <t>206/504</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -924,7 +926,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -951,7 +953,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -961,7 +963,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -971,7 +973,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>141/505</t>
+          <t>140/504</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -981,7 +983,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>139/505</t>
+          <t>138/504</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -996,7 +998,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1023,7 +1025,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1033,7 +1035,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1043,7 +1045,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>203/505</t>
+          <t>202/504</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1053,7 +1055,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>125/505</t>
+          <t>124/504</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1063,17 +1065,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>MetaModelFmin2</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.7471</t>
+          <t>0.7431</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1097,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1105,7 +1107,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1115,7 +1117,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>356/505</t>
+          <t>355/504</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1125,7 +1127,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>388/505</t>
+          <t>387/504</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1135,17 +1137,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>CMAL3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0.7430</t>
+          <t>0.7256</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1169,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1177,7 +1179,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1187,7 +1189,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111/505</t>
+          <t>111/504</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1197,7 +1199,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87/505</t>
+          <t>87/504</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1212,7 +1214,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1239,7 +1241,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1249,7 +1251,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1259,7 +1261,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>98/505</t>
+          <t>98/504</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1269,7 +1271,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60/505</t>
+          <t>60/504</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1284,7 +1286,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1311,7 +1313,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1321,7 +1323,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1331,7 +1333,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>104/505</t>
+          <t>104/504</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1341,7 +1343,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179/505</t>
+          <t>179/504</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1356,7 +1358,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1383,7 +1385,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1393,7 +1395,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1403,7 +1405,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>385/505</t>
+          <t>384/504</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1413,7 +1415,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>390/505</t>
+          <t>389/504</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1429,7 +1431,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1456,57 +1458,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>103/505</t>
+          <t>102/504</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198.2</t>
+          <t>-198.2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61/505</t>
+          <t>60/504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>199.8</t>
+          <t>-199.8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>250/505</t>
+          <t>249/504</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>188.2</t>
+          <t>-188.2</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>268/505</t>
+          <t>267/504</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>184.6</t>
+          <t>-184.6</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>CMAL3</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>208.4</t>
+          <t>-206.2</t>
         </is>
       </c>
     </row>
@@ -1528,42 +1530,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>140/505</t>
+          <t>140/504</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>-145.3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90/505</t>
+          <t>90/504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>-147.8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>133/505</t>
+          <t>133/504</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>-146.0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>139/505</t>
+          <t>139/504</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145.4</t>
+          <t>-145.4</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1573,12 +1575,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>154.3</t>
+          <t>-154.3</t>
         </is>
       </c>
     </row>
@@ -1600,42 +1602,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164/505</t>
+          <t>164/504</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137.1</t>
+          <t>-137.1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88/505</t>
+          <t>88/504</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>139.1</t>
+          <t>-139.1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>118/505</t>
+          <t>118/504</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>137.6</t>
+          <t>-137.6</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153/505</t>
+          <t>153/504</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>-137.4</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1645,12 +1647,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>143.4</t>
+          <t>-143.4</t>
         </is>
       </c>
     </row>
@@ -1672,57 +1674,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80/505</t>
+          <t>79/504</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>411.1</t>
+          <t>-411.1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90/505</t>
+          <t>89/504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>410.4</t>
+          <t>-410.4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>265/505</t>
+          <t>264/504</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>379.4</t>
+          <t>-379.4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>267/505</t>
+          <t>266/504</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>377.5</t>
+          <t>-377.5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>ChainCMAwithRsqrt</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>438.1</t>
+          <t>-430.7</t>
         </is>
       </c>
     </row>
@@ -1744,42 +1746,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>130/505</t>
+          <t>129/504</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323.6</t>
+          <t>-323.6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80/505</t>
+          <t>80/504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>329.7</t>
+          <t>-329.7</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>265/505</t>
+          <t>264/504</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>311.7</t>
+          <t>-311.7</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>276/505</t>
+          <t>275/504</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>309.7</t>
+          <t>-309.7</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1789,12 +1791,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>344.2</t>
+          <t>-344.2</t>
         </is>
       </c>
     </row>
@@ -1816,42 +1818,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>138/505</t>
+          <t>137/504</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>304.4</t>
+          <t>-304.4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66/505</t>
+          <t>65/504</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>-310.0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>242/505</t>
+          <t>241/504</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>298.3</t>
+          <t>-298.3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>261/505</t>
+          <t>260/504</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>295.9</t>
+          <t>-295.9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1861,12 +1863,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>319.3</t>
+          <t>-319.3</t>
         </is>
       </c>
     </row>
@@ -1888,57 +1890,58 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47/504</t>
+          <t>46/503</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>577.1</t>
+          <t>-577.1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65/504</t>
+          <t>64/503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>570.8</t>
+          <t>-570.8</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>256/504</t>
+          <t>255/503</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>504.4</t>
+          <t>-504.4</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>224/504</t>
+          <t>223/503</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>517.2</t>
+          <t>-517.2</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>DiscreteLengler2On
+ePlusOne</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>588.7</t>
+          <t>-587.7</t>
         </is>
       </c>
     </row>
@@ -1960,42 +1963,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30/505</t>
+          <t>30/504</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>436.5</t>
+          <t>-436.5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20/505</t>
+          <t>20/504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>438.3</t>
+          <t>-438.3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>242/505</t>
+          <t>241/504</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>408.4</t>
+          <t>-408.4</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>227/505</t>
+          <t>226/504</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>413.0</t>
+          <t>-413.0</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2005,12 +2008,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>453.8</t>
+          <t>-453.8</t>
         </is>
       </c>
     </row>
@@ -2032,42 +2035,42 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29/505</t>
+          <t>29/504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>425.0</t>
+          <t>-425.0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18/505</t>
+          <t>18/504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>427.5</t>
+          <t>-427.5</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>238/505</t>
+          <t>237/504</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>398.9</t>
+          <t>-398.9</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>223/505</t>
+          <t>222/504</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>403.7</t>
+          <t>-403.7</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2077,12 +2080,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>435.4</t>
+          <t>-435.4</t>
         </is>
       </c>
     </row>
@@ -2104,57 +2107,57 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>48/505</t>
+          <t>47/504</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1193.3</t>
+          <t>-1193.3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79/505</t>
+          <t>78/504</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1177.9</t>
+          <t>-1177.9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>258/505</t>
+          <t>257/504</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1034.7</t>
+          <t>-1034.7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>254/505</t>
+          <t>253/504</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1046.1</t>
+          <t>-1046.1</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Tabu</t>
+          <t>NgIoh</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1216.2</t>
+          <t>-1207.2</t>
         </is>
       </c>
     </row>
@@ -2176,42 +2179,42 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19/505</t>
+          <t>19/504</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>932.9</t>
+          <t>-932.9</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16/505</t>
+          <t>16/504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>934.5</t>
+          <t>-934.5</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>266/505</t>
+          <t>265/504</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>842.8</t>
+          <t>-842.8</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>254/505</t>
+          <t>253/504</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>857.3</t>
+          <t>-857.3</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2221,12 +2224,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>964.9</t>
+          <t>-964.9</t>
         </is>
       </c>
     </row>
@@ -2248,42 +2251,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20/505</t>
+          <t>19/504</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>912.6</t>
+          <t>-912.6</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54/505</t>
+          <t>53/504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>907.6</t>
+          <t>-907.6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>264/505</t>
+          <t>263/504</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>817.2</t>
+          <t>-817.2</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>250/505</t>
+          <t>249/504</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>830.9</t>
+          <t>-830.9</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2293,12 +2296,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>928.6</t>
+          <t>-928.6</t>
         </is>
       </c>
     </row>
@@ -2320,42 +2323,42 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1623.5</t>
+          <t>-1623.5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46/505</t>
+          <t>46/504</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1570.4</t>
+          <t>-1570.4</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>199/505</t>
+          <t>199/504</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1317.4</t>
+          <t>-1317.4</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>99/505</t>
+          <t>99/504</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1422.4</t>
+          <t>-1422.4</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2365,12 +2368,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1607.1</t>
+          <t>-1607.1</t>
         </is>
       </c>
     </row>
@@ -2392,42 +2395,42 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1300.4</t>
+          <t>-1300.4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1290.5</t>
+          <t>-1290.5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>197/505</t>
+          <t>197/504</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1105.2</t>
+          <t>-1105.2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>92/505</t>
+          <t>92/504</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1197.0</t>
+          <t>-1197.0</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2438,12 +2441,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1301.4</t>
+          <t>-1301.4</t>
         </is>
       </c>
     </row>
@@ -2465,42 +2468,42 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1234.7</t>
+          <t>-1234.7</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12/505</t>
+          <t>12/504</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1230.9</t>
+          <t>-1230.9</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>187/505</t>
+          <t>187/504</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1073.0</t>
+          <t>-1073.0</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>92/505</t>
+          <t>92/504</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1154.4</t>
+          <t>-1154.4</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2511,12 +2514,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1233.8</t>
+          <t>-1233.8</t>
         </is>
       </c>
     </row>
@@ -2538,42 +2541,42 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3/505</t>
+          <t>3/504</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3285.9</t>
+          <t>-3285.9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53/505</t>
+          <t>53/504</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3208.6</t>
+          <t>-3208.6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>196/505</t>
+          <t>196/504</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2650.7</t>
+          <t>-2650.7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>148/505</t>
+          <t>148/504</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2854.3</t>
+          <t>-2854.3</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2583,12 +2586,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3316.5</t>
+          <t>-3316.5</t>
         </is>
       </c>
     </row>
@@ -2610,42 +2613,42 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2633.4</t>
+          <t>-2633.4</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35/505</t>
+          <t>35/504</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2597.5</t>
+          <t>-2597.5</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>208/505</t>
+          <t>208/504</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2219.0</t>
+          <t>-2219.0</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>134/505</t>
+          <t>134/504</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2391.5</t>
+          <t>-2391.5</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2656,12 +2659,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2617.0</t>
+          <t>-2617.0</t>
         </is>
       </c>
     </row>
@@ -2683,42 +2686,42 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1/505</t>
+          <t>1/504</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2606.9</t>
+          <t>-2606.9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>41/505</t>
+          <t>41/504</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2557.0</t>
+          <t>-2557.0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>185/505</t>
+          <t>185/504</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2206.6</t>
+          <t>-2206.6</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>141/505</t>
+          <t>141/504</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2349.2</t>
+          <t>-2349.2</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2729,12 +2732,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2/505</t>
+          <t>2/504</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2605.1</t>
+          <t>-2605.1</t>
         </is>
       </c>
     </row>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -591,57 +591,57 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7106</t>
+          <t>0.7124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0.7096</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>126/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0.7050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>236/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0.7009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0.7119</t>
+          <t>0.7126</t>
         </is>
       </c>
     </row>
@@ -663,57 +663,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7429</t>
+          <t>0.7471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0.7391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>146/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0.7317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>204/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0.7274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0.7459</t>
+          <t>0.7497</t>
         </is>
       </c>
     </row>
@@ -735,58 +735,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.7504</t>
+          <t>0.7606</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0.7463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>146/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0.7330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>179/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0.7311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ChainCMAwithMetaRe
-centeringsqrt</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0.7565</t>
+          <t>0.7658</t>
         </is>
       </c>
     </row>
@@ -808,58 +807,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7396</t>
+          <t>0.7565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.7330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>262/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0.7088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>308/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0.6932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>ChainCMAwithLHSsqr
-t</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0.7493</t>
+          <t>0.7535</t>
         </is>
       </c>
     </row>
@@ -881,57 +879,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.7098</t>
+          <t>0.7119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0.7061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>158/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0.6959</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>206/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0.6941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0.7075</t>
+          <t>0.7094</t>
         </is>
       </c>
     </row>
@@ -953,57 +951,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7344</t>
+          <t>0.7410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0.7305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>140/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0.7138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>138/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0.7139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0.7304</t>
+          <t>0.7364</t>
         </is>
       </c>
     </row>
@@ -1025,57 +1023,57 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7555</t>
+          <t>0.7665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0.7465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>202/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0.7191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>124/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0.7252</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>MetaModelFmin2</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0.7431</t>
+          <t>0.7535</t>
         </is>
       </c>
     </row>
@@ -1097,57 +1095,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.7353</t>
+          <t>0.7436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0.7266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>355/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0.6372</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>387/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0.6071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0.7256</t>
+          <t>0.7373</t>
         </is>
       </c>
     </row>
@@ -1169,57 +1167,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.7072</t>
+          <t>0.7092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0.7014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>111/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0.6810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0.6869</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0.6989</t>
+          <t>0.7029</t>
         </is>
       </c>
     </row>
@@ -1241,57 +1239,58 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.7343</t>
+          <t>0.7403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0.7249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>98/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0.7004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0.7100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>MetaModelFmin2</t>
+          <t>HugeLognormalDiscr
+eteOnePlusOne</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0.7218</t>
+          <t>0.7269</t>
         </is>
       </c>
     </row>
@@ -1313,57 +1312,58 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.7477</t>
+          <t>0.7587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0.7336</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>104/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0.7007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0.6895</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>MetaModelFmin2</t>
+          <t>HugeLognormalDiscr
+eteOnePlusOne</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.7295</t>
+          <t>0.7352</t>
         </is>
       </c>
     </row>
@@ -1385,58 +1385,59 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.7248</t>
+          <t>0.7290</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0.7171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>384/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0.5798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>389/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0.5730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>LognormalDiscreteO
-nePlusOne</t>
+          <t>OnePtRecombiningDi
+screteLenglerOnePl
+usOne</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.7166</t>
+          <t>0.7242</t>
         </is>
       </c>
     </row>
@@ -1458,57 +1459,57 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>102/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-198.2</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-199.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>249/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-188.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>267/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-184.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-206.2</t>
+          <t>212.2</t>
         </is>
       </c>
     </row>
@@ -1530,57 +1531,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>140/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-145.3</t>
+          <t>151.9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-147.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>133/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-146.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>139/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-145.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-154.3</t>
+          <t>154.6</t>
         </is>
       </c>
     </row>
@@ -1602,42 +1603,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-137.1</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-139.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>118/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-137.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-137.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1647,12 +1648,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-143.4</t>
+          <t>144.7</t>
         </is>
       </c>
     </row>
@@ -1674,57 +1675,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-411.1</t>
+          <t>429.0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-410.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>264/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-379.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>266/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-377.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>ChainCMAwithRsqrt</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-430.7</t>
+          <t>445.3</t>
         </is>
       </c>
     </row>
@@ -1746,57 +1747,57 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>129/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-323.6</t>
+          <t>338.6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-329.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>264/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>-311.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>275/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-309.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-344.2</t>
+          <t>345.5</t>
         </is>
       </c>
     </row>
@@ -1818,57 +1819,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>137/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-304.4</t>
+          <t>316.4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-310.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>241/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-298.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>260/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-295.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-319.3</t>
+          <t>326.1</t>
         </is>
       </c>
     </row>
@@ -1890,58 +1891,57 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46/503</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-577.1</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64/503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-570.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>255/503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-504.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>223/503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-517.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>DiscreteLengler2On
-ePlusOne</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1/503</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-587.7</t>
+          <t>616.4</t>
         </is>
       </c>
     </row>
@@ -1963,57 +1963,57 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-436.5</t>
+          <t>451.1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-438.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>241/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-408.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>226/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-413.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-453.8</t>
+          <t>465.8</t>
         </is>
       </c>
     </row>
@@ -2035,57 +2035,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-425.0</t>
+          <t>438.4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-427.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>237/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-398.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>222/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-403.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-435.4</t>
+          <t>451.9</t>
         </is>
       </c>
     </row>
@@ -2107,57 +2107,57 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>47/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1193.3</t>
+          <t>1232.9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1177.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>257/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1034.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>253/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1046.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>NgIoh</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-1207.2</t>
+          <t>1280.2</t>
         </is>
       </c>
     </row>
@@ -2179,57 +2179,57 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>19/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-932.9</t>
+          <t>964.8</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-934.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>265/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>-842.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>253/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-857.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>CMApara</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-964.9</t>
+          <t>994.7</t>
         </is>
       </c>
     </row>
@@ -2251,57 +2251,57 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19/504</t>
+          <t>3/80</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-912.6</t>
+          <t>937.6</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-907.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>263/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-817.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>249/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-830.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>CMAL3</t>
+          <t>DiscreteDE</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-928.6</t>
+          <t>967.3</t>
         </is>
       </c>
     </row>
@@ -2323,57 +2323,58 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>27/80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1623.5</t>
+          <t>1671.7</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-1570.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>199/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-1317.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>99/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1422.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>NLOPT_LN_PRAXIS</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-1607.1</t>
+          <t>1694.5</t>
         </is>
       </c>
     </row>
@@ -2395,58 +2396,58 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1300.4</t>
+          <t>1340.8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1290.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>197/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1105.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>92/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1197.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>BigLognormalDiscre
-teOnePlusOne</t>
+          <t>HugeLognormalDiscr
+eteOnePlusOne</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>2/80</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-1301.4</t>
+          <t>1340.1</t>
         </is>
       </c>
     </row>
@@ -2468,58 +2469,58 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>22/80</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-1234.7</t>
+          <t>1264.0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-1230.9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>187/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-1073.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>92/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1154.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SVMMetaModelLogNor
-mal</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-1233.8</t>
+          <t>1293.5</t>
         </is>
       </c>
     </row>
@@ -2541,57 +2542,58 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3/504</t>
+          <t>40/80</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3285.9</t>
+          <t>3376.6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3208.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>196/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2650.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>148/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2854.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>RLSOnePlusOne</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-3316.5</t>
+          <t>3453.3</t>
         </is>
       </c>
     </row>
@@ -2613,58 +2615,58 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>3/80</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2633.4</t>
+          <t>2706.1</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>35/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-2597.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>208/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>-2219.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>134/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2391.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>DiscreteLengler2On
-ePlusOne</t>
+          <t>HugeLognormalDiscr
+eteOnePlusOne</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-2617.0</t>
+          <t>2717.2</t>
         </is>
       </c>
     </row>
@@ -2686,58 +2688,58 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1/504</t>
+          <t>12/80</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2606.9</t>
+          <t>2672.3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>41/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2557.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>185/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2206.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>141/504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2349.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SVM1MetaModelLogNo
-rmal</t>
+          <t>HugeLognormalDiscr
+eteOnePlusOne</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2/504</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-2605.1</t>
+          <t>2712.2</t>
         </is>
       </c>
     </row>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7124</t>
+          <t>0.7123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7471</t>
+          <t>0.7470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.7606</t>
+          <t>0.7599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7565</t>
+          <t>0.7558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7410</t>
+          <t>0.7412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7665</t>
+          <t>0.7667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.7436</t>
+          <t>0.7434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.7092</t>
+          <t>0.7093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.7403</t>
+          <t>0.7402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.7587</t>
+          <t>0.7573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.7290</t>
+          <t>0.7278</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>206.6</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151.9</t>
+          <t>152.8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>429.0</t>
+          <t>425.2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316.4</t>
+          <t>317.6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>595.2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>451.1</t>
+          <t>451.3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438.4</t>
+          <t>439.5</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1232.9</t>
+          <t>1229.2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/80</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>964.8</t>
+          <t>958.3</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>937.6</t>
+          <t>936.4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>27/80</t>
+          <t>28/80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1671.7</t>
+          <t>1670.5</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1340.8</t>
+          <t>1345.3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22/80</t>
+          <t>17/80</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1264.0</t>
+          <t>1267.8</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3376.6</t>
+          <t>3371.3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2706.1</t>
+          <t>2692.2</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12/80</t>
+          <t>31/80</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2672.3</t>
+          <t>2656.0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7123</t>
+          <t>0.7122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7470</t>
+          <t>0.7471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.7599</t>
+          <t>0.7609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7558</t>
+          <t>0.7546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.7119</t>
+          <t>0.7120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7412</t>
+          <t>0.7418</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7667</t>
+          <t>0.7683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.7434</t>
+          <t>0.7429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.7093</t>
+          <t>0.7092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.7402</t>
+          <t>0.7400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.7573</t>
+          <t>0.7585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.7278</t>
+          <t>0.7287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>206.6</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152.8</t>
+          <t>151.1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/80</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>141.9</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>425.2</t>
+          <t>423.9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338.6</t>
+          <t>337.9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>317.6</t>
+          <t>317.1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>595.2</t>
+          <t>594.4</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>451.3</t>
+          <t>452.2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/80</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>439.5</t>
+          <t>437.9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>4/80</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1229.2</t>
+          <t>1221.2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>958.3</t>
+          <t>960.0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>936.4</t>
+          <t>942.4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28/80</t>
+          <t>34/80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1670.5</t>
+          <t>1668.9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1345.3</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>17/80</t>
+          <t>12/80</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1267.8</t>
+          <t>1272.5</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3371.3</t>
+          <t>3380.1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2692.2</t>
+          <t>2704.6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>31/80</t>
+          <t>38/80</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2656.0</t>
+          <t>2640.6</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1444,7 +1444,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>0.7904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7659</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7651</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1504,19 +1504,19 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>0.7918</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151.1</t>
+          <t>0.8209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1551,22 +1551,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51/83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7825</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7793</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1576,19 +1576,19 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>154.6</t>
+          <t>0.8154</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1598,17 +1598,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>0.8035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1623,22 +1623,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7645</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58/83</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7548</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>0.8033</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>14/83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>423.9</t>
+          <t>0.7622</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1695,22 +1695,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59/83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6583</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1720,39 +1720,39 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>445.3</t>
+          <t>0.7779</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>337.9</t>
+          <t>0.7979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48/83</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7600</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50/83</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7530</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1792,39 +1792,39 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>345.5</t>
+          <t>0.7918</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>317.1</t>
+          <t>0.8102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1839,22 +1839,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48/83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7621</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7523</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>326.1</t>
+          <t>0.7959</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>594.4</t>
+          <t>0.7901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1911,44 +1911,46 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7469</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7322</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>RandRecombiningDis
+creteLenglerOnePlu
+sOne</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>616.4</t>
+          <t>0.7829</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1958,17 +1960,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>44/83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>452.2</t>
+          <t>0.7449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1983,64 +1985,66 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63/83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6098</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58/83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6297</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>OnePtRecombiningDi
+screteLenglerOnePl
+usOne</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>465.8</t>
+          <t>0.7618</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>437.9</t>
+          <t>0.7871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2055,64 +2059,65 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47/83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7363</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49/83</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7243</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>451.9</t>
+          <t>0.7741</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1221.2</t>
+          <t>0.7964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2127,49 +2132,50 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47/83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7393</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49/83</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7246</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1280.2</t>
+          <t>0.7839</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2179,12 +2185,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>31/83</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>0.7704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2199,64 +2205,65 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47/83</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7265</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7064</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>DiscreteLengler3On
+ePlusOne</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>994.7</t>
+          <t>0.7783</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>QUBO</t>
+          <t>NK3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>256</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>46/83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>942.4</t>
+          <t>0.7266</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2271,37 +2278,38 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63/83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5784</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62/83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5798</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>DiscreteDE</t>
+          <t>SmallLognormalDisc
+reteOnePlusOne</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>967.3</t>
+          <t>0.7552</t>
         </is>
       </c>
     </row>
@@ -2313,431 +2321,1295 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>205.5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>212.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>151.1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>154.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3/80</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>141.9</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>423.9</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>445.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>337.9</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>345.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>317.1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>326.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>594.4</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>616.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2/80</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>452.2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>465.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3/80</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>437.9</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>451.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>4/80</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1221.2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>1280.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3/80</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>994.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>3/80</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>942.4</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>DiscreteDE</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>967.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUBO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>34/80</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1668.9</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>DiscreteLengler3On
 ePlusOne</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>1694.5</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1344.9</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>HugeLognormalDiscr
 eteOnePlusOne</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>2/80</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>1340.1</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>12/80</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1272.5</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>DiscreteLengler3On
 ePlusOne</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>1293.5</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>40/80</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>3380.1</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>DiscreteLengler3On
 ePlusOne</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>3453.3</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>3/80</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>2704.6</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>HugeLognormalDiscr
 eteOnePlusOne</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>2717.2</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>QUBO</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>38/80</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>2640.6</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>HugeLognormalDiscr
 eteOnePlusOne</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>2712.2</t>
         </is>

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36/83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7097</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7052</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7008</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -673,32 +673,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7412</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53/83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7312</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7262</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,32 +745,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4/83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7330</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7316</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -817,32 +817,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8/83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7368</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7176</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7174</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -889,32 +889,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7085</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6956</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6928</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -961,32 +961,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7334</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7147</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7135</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1033,32 +1033,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7514</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7229</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53/83</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7285</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1105,32 +1105,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7369</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7034</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6681</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1177,32 +1177,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7048</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6802</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50/83</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1249,32 +1249,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7314</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6989</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48/83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7093</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1322,32 +1322,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7429</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7019</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47/83</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7162</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.7315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.6805</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62/83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5852</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0.7322</t>
+          <t>0.7321</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0.7243</t>
+          <t>0.7238</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0.7246</t>
+          <t>0.7249</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0.7064</t>
+          <t>0.7072</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0.5798</t>
+          <t>0.5790</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2341,32 +2341,32 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24/83</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>200.7</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187.9</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59/83</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184.2</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2413,32 +2413,32 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5/83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25/83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46/83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13/83</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139.6</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46/83</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45/83</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2557,32 +2557,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36/83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412.8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59/83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375.6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58/83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379.7</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2629,32 +2629,32 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5/83</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330.2</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313.7</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313.8</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19/83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310.6</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297.3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58/83</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>296.7</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2773,32 +2773,32 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18/83</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>585.8</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505.2</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511.8</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4/83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445.5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410.9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412.6</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2917,32 +2917,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11/83</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430.5</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402.5</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405.8</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4/80</t>
+          <t>4/83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2989,32 +2989,32 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15/83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1211.7</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1030.1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1048.9</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3061,32 +3061,32 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7/83</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>936.2</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>841.7</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55/83</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865.7</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3133,32 +3133,32 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>928.4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>818.9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>829.0</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>34/80</t>
+          <t>35/83</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3205,32 +3205,32 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16/83</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1680.4</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1327.4</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53/83</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1418.7</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3278,32 +3278,32 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7/83</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1322.3</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1102.8</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51/83</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1191.6</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2/80</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>12/80</t>
+          <t>13/83</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3351,32 +3351,32 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11/83</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1277.8</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51/83</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1146.9</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>40/80</t>
+          <t>41/83</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29/83</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3406.7</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2646.0</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2881.9</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3/80</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3497,32 +3497,32 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7/83</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2656.3</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56/83</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2245.8</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54/83</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2399.2</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>38/80</t>
+          <t>39/83</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7/83</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2681.7</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57/83</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2177.0</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53/83</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2362.4</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.7122</t>
+          <t>0.7124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.7471</t>
+          <t>0.7475</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.7546</t>
+          <t>0.7538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.7120</t>
+          <t>0.7118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.7418</t>
+          <t>0.7406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.7683</t>
+          <t>0.7646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.7429</t>
+          <t>0.7454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.7092</t>
+          <t>0.7091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.7400</t>
+          <t>0.7395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.7585</t>
+          <t>0.7598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>1/83</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0.7334</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>2/83</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0.7287</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1/83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0.7904</t>
+          <t>0.7894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0.8209</t>
+          <t>0.8204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0.8035</t>
+          <t>0.8066</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0.7622</t>
+          <t>0.7627</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0.7979</t>
+          <t>0.7975</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0.8102</t>
+          <t>0.8123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0.7901</t>
+          <t>0.7989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0.7449</t>
+          <t>0.7491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0.7871</t>
+          <t>0.7889</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0.7964</t>
+          <t>0.8035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>31/83</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0.7704</t>
+          <t>0.7823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0.7266</t>
+          <t>0.7285</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>205.2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>151.1</t>
+          <t>151.2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141.9</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>423.9</t>
+          <t>425.5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>337.9</t>
+          <t>337.0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>317.1</t>
+          <t>316.2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>6/83</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>594.4</t>
+          <t>590.2</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>452.2</t>
+          <t>449.2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>437.9</t>
+          <t>438.7</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1221.2</t>
+          <t>1224.2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>958.7</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>5/83</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>942.4</t>
+          <t>931.3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>35/83</t>
+          <t>21/83</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1668.9</t>
+          <t>1677.1</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>3/83</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>1331.5</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>13/83</t>
+          <t>4/83</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1272.5</t>
+          <t>1282.0</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11/83</t>
+          <t>12/83</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3380.1</t>
+          <t>3392.4</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>1/83</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2704.6</t>
+          <t>2717.3</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>2/83</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>39/83</t>
+          <t>21/83</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2640.6</t>
+          <t>2666.0</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36/83</t>
+          <t>36/84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10/83</t>
+          <t>10/84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53/83</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4/83</t>
+          <t>4/84</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8/83</t>
+          <t>8/84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>53/83</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50/83</t>
+          <t>50/84</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48/83</t>
+          <t>48/84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47/83</t>
+          <t>47/84</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62/83</t>
+          <t>63/84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24/83</t>
+          <t>24/84</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>57/83</t>
+          <t>57/84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>59/83</t>
+          <t>59/84</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5/83</t>
+          <t>5/84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25/83</t>
+          <t>25/84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>46/83</t>
+          <t>46/84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13/83</t>
+          <t>13/84</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>46/83</t>
+          <t>46/84</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>45/83</t>
+          <t>45/84</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36/83</t>
+          <t>36/84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59/83</t>
+          <t>59/84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>58/83</t>
+          <t>58/84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5/83</t>
+          <t>5/84</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>57/83</t>
+          <t>57/84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19/83</t>
+          <t>19/84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>58/83</t>
+          <t>58/84</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6/83</t>
+          <t>6/84</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18/83</t>
+          <t>18/84</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4/83</t>
+          <t>4/84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11/83</t>
+          <t>11/84</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4/83</t>
+          <t>4/84</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15/83</t>
+          <t>15/84</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>57/83</t>
+          <t>57/84</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7/83</t>
+          <t>7/84</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>55/83</t>
+          <t>55/84</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5/83</t>
+          <t>5/84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10/83</t>
+          <t>10/84</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>21/83</t>
+          <t>21/84</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16/83</t>
+          <t>16/84</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>53/83</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3/83</t>
+          <t>3/84</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7/83</t>
+          <t>7/84</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>51/83</t>
+          <t>51/84</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>4/83</t>
+          <t>4/84</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12/83</t>
+          <t>12/84</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>51/83</t>
+          <t>51/84</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>41/83</t>
+          <t>41/84</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>29/83</t>
+          <t>29/84</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>57/83</t>
+          <t>57/84</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7/83</t>
+          <t>7/84</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>56/83</t>
+          <t>56/84</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>54/83</t>
+          <t>54/84</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2/83</t>
+          <t>2/84</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>21/83</t>
+          <t>21/84</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7/83</t>
+          <t>7/84</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>57/83</t>
+          <t>57/84</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>53/83</t>
+          <t>53/84</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1/83</t>
+          <t>1/84</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">

--- a/courbes/summary_table.xlsx
+++ b/courbes/summary_table.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2313,1308 +2313,6 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>205.2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24/84</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>200.7</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>57/84</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>187.9</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>59/84</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>184.2</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>212.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>151.2</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>5/84</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>149.7</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>25/84</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>145.7</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>46/84</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>154.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>3/84</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>141.7</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>13/84</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>139.6</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>46/84</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>45/84</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>144.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>425.5</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>36/84</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>412.8</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>59/84</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>375.6</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>58/84</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>379.7</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>445.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>337.0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5/84</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>330.2</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>57/84</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>313.7</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>313.8</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>345.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>316.2</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>19/84</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>310.6</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>297.3</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>58/84</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>296.7</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>326.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>6/84</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>590.2</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>18/84</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>585.8</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>505.2</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>511.8</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>616.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>449.2</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4/84</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>445.5</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>55/84</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>410.9</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>412.6</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>465.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>438.7</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>11/84</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>430.5</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>402.5</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>405.8</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>451.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>4/84</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1224.2</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>15/84</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1211.7</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>57/84</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>1030.1</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>1048.9</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1280.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>3/84</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>958.7</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>7/84</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>936.2</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>841.7</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>55/84</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>865.7</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>994.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>5/84</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>931.3</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>10/84</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>928.4</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>818.9</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>829.0</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteDE</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>967.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>21/84</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1677.1</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>16/84</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1680.4</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>1327.4</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>53/84</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>1418.7</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteLengler3On
-ePlusOne</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1694.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>3/84</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1331.5</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>7/84</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1322.3</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1102.8</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>51/84</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1191.6</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>HugeLognormalDiscr
-eteOnePlusOne</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1340.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>4/84</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1282.0</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>12/84</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>1277.8</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>1085.0</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>51/84</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>1146.9</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteLengler3On
-ePlusOne</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1293.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>41/84</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>3392.4</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>29/84</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>3406.7</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>57/84</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2646.0</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>2881.9</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>DiscreteLengler3On
-ePlusOne</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>3453.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>2717.3</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>7/84</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>2656.3</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>56/84</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2245.8</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>54/84</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>2399.2</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>HugeLognormalDiscr
-eteOnePlusOne</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2/84</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>2717.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>QUBO</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>21/84</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>2666.0</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>7/84</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2681.7</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>57/84</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>2177.0</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>53/84</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>2362.4</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>HugeLognormalDiscr
-eteOnePlusOne</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1/84</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>2712.2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="L1:N1"/>
